--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T02:00:44+00:00</t>
+    <t>2026-06-17T06:24:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T06:24:13+00:00</t>
+    <t>2026-06-17T09:04:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:04:26+00:00</t>
+    <t>2026-06-17T09:15:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
